--- a/docs/downloads/04/tbl_other_chars_alaotra_avaradrano.xlsx
+++ b/docs/downloads/04/tbl_other_chars_alaotra_avaradrano.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,12 +438,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -651,12 +645,6 @@
           <t>En concubinage</t>
         </is>
       </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -671,14 +659,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E15">
-        <v>8.9</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="16">
@@ -694,14 +682,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="E16">
-        <v>5.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="17">
@@ -717,20 +705,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>38.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -740,14 +728,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>284</v>
       </c>
       <c r="E18">
-        <v>4.1</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="19">
@@ -763,14 +751,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D19">
-        <v>284</v>
+        <v>37</v>
       </c>
       <c r="E19">
-        <v>38.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -786,14 +774,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -809,14 +797,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="E21">
-        <v>3.4</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="22">
@@ -832,14 +820,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D22">
-        <v>93</v>
+        <v>272</v>
       </c>
       <c r="E22">
-        <v>12.5</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="23">
@@ -855,59 +843,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E23">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>272</v>
-      </c>
-      <c r="E24">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>15</v>
-      </c>
-      <c r="E25">
         <v>2</v>
       </c>
     </row>
